--- a/DataRepo/data/tests/small_obob/small_obob_animal_and_sample_table.xlsx
+++ b/DataRepo/data/tests/small_obob/small_obob_animal_and_sample_table.xlsx
@@ -1,30 +1,160 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/small_obob/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57513DA5-5149-DF40-A220-1661542BA72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78474804-941F-6B45-92A5-24FF911A5915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12180" yWindow="1520" windowWidth="29900" windowHeight="20220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12180" yWindow="1520" windowWidth="29900" windowHeight="20220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Animals" sheetId="1" r:id="rId1"/>
-    <sheet name="Samples" sheetId="2" r:id="rId2"/>
-    <sheet name="Treatments" sheetId="3" r:id="rId3"/>
-    <sheet name="Tissues" sheetId="4" r:id="rId4"/>
+    <sheet name="Study" sheetId="9" r:id="rId1"/>
+    <sheet name="Animals" sheetId="1" r:id="rId2"/>
+    <sheet name="Samples" sheetId="2" r:id="rId3"/>
+    <sheet name="Sequences" sheetId="8" r:id="rId4"/>
     <sheet name="Peak Annotation Files" sheetId="6" r:id="rId5"/>
-    <sheet name="Infusions" sheetId="5" r:id="rId6"/>
+    <sheet name="Peak Annotation Details" sheetId="7" r:id="rId6"/>
+    <sheet name="Treatments" sheetId="3" r:id="rId7"/>
+    <sheet name="Tissues" sheetId="4" r:id="rId8"/>
+    <sheet name="Infusions" sheetId="5" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>TraceBase Dev Team</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{C8F73FAE-0063-184D-AE84-904817F8C9D8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">A 2 to 6 character unique readable alphanumeric code for the study, to be used
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">as a prefix for animal names, sample names, etc if necessary, to make them
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">unique.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Must be unique.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Optional.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{9DD3C0F6-643F-C646-9957-604AAD2D5A2E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>A succinct name for the study, which is a collection of one or more series of
+animals and their associated data.
+Must be unique.
+Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{13ED60A2-33CC-984B-A004-5ADFF55D03F9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>A long form description for the study which may include the experimental design
+process, citations, and other relevant details.
+Optional.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -192,7 +322,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -291,10 +421,18 @@
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
             <family val="2"/>
-            <scheme val="minor"/>
           </rPr>
-          <t>Unique identifier for the animal (mouse) the sample was collected from. MUST match the Animal ID in the Animal Table.
-	-Lance Parsons</t>
+          <t xml:space="preserve">Unique identifier for the animal (mouse) the sample was collected from. MUST match the Animal ID in the Animal Table.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">	-Lance Parsons</t>
         </r>
       </text>
     </comment>
@@ -302,7 +440,646 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>TraceBase Dev Team</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{BA594A13-C096-E648-A909-5EA315C2027A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Readonly.  (Calculated by formula.)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Read-only. (Calculated by formula).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">A unique sequence identifier.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Note that a sequence record is unique to a researcher, protocol, instrument
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">model, and date.  If a researcher performs multiple such Mass Spec runs on the
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">same day, this sequence record will represent multiple runs.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">This column is used to populate Sequence Name choices in the Peak Annotation
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Details sheet.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Comma-delimited string combining the values from these columns in this order:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- Operator
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- LC Protocol Name
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- Instrument
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">- Date
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{1EA521C2-020B-9F46-A820-B9976CA1DF2F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Researcher who operated the Mass Spec instrument.
+Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{A5F50F62-FBF1-7D40-AA60-C5F377B8509F}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Unique laboratory-defined name of the liquid chromatography method.(e.g. polar-
+HILIC-25-min)
+Select a 'LC Protocol Name' from the dropdowns in this column.  The dropdowns
+are populated by the 'Name' column in the 'LC Protocols' sheet, so if the
+dropdowns are empty, add rows to the 'LC Protocols' sheet.
+Must be unique.
+Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{E1153B1B-1884-F747-9FE9-4F7A7E59CCA5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>The name of the mass spectrometer.
+Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{4A40E0E3-93EE-3C44-9665-322464D3B0D9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">The date that the mass spectrometer was run.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Format: YYYY-MM-DD.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{3E5856A4-F467-FF4C-A644-A2B06F3179B0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Notes on this mass spectrometer run sequence.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Must be unique.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Optional.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>TraceBase Dev Team</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{CE64C618-F29B-424B-9E2B-4759D1D50CB3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">A sample that was injected at least once during a mass spectrometer sequence.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Select a 'Sample Name' from the dropdowns in this column.  The dropdowns are
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">populated by the 'Sample' column in the 'Samples' sheet, so if the dropdowns are
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">empty, add rows to the 'Samples' sheet.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{3E8E86B8-003F-B24B-9DC9-6D0A3211D678}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sample header from Peak Annotation File Name.
+Required.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{78ECA8BA-6272-844B-9091-88941D611C5B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>A file representing a subset of data extracted from the raw file (e.g. an mzXML
+file).
+Optional.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{F6A3EF04-F3BD-0A45-B669-0FB9B4EFE55A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Name of the accucor or isocorr file that this sample was analyzed in, if any.
+If the sample on this row was included in a Peak Annotation File Name, add the
+name of that file here.  If you are loading an mzXML File Name that was not used
+in a Peak Annotation File Name, leave this value empty.
+Note, you do not need to have an mzXML File Name associated with every Sample
+Data Header from a Peak Annotation File Name worked out ahead of time.  That
+association can be made at a later date.
+Select a 'Peak Annotation File Name' from the dropdowns in this column.  The
+dropdowns are populated by the 'Peak Annotation File' column in the 'Peak
+Annotation Files' sheet, so if the dropdowns are empty, add rows to the 'Peak
+Annotation Files' sheet.
+Optional.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{C98875B1-996F-DE4C-BDD9-A095939013A2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color indexed="81"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>The MSRun Sequence associated with the Sample Name, Sample Data Header, and/or
+mzXML File Name on this row.
+Comma-delimited string combining the values from these columns from the
+Sequences sheet in this order:
+- Operator
+- LC Protocol Name
+- Instrument
+- Date
+Select a 'Sequence Name' from the dropdowns in this column.  The dropdowns are
+populated by the 'Sequence Name' column in the 'Sequences' sheet, so if the
+dropdowns are empty, add rows to the 'Sequences' sheet.
+Optional.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{7335DF1F-904A-1448-AB21-45B4A8BDCD73}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Whether to load data associated with this sample, e.g. a blank sample.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Enter 'skip' to skip loading of the sample and peak annotation data.  The mzXML
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">file will be saved if supplied, but it will not be associated with an
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">MSRunSample or MSRunSequence, since the Sample record will not be created.  Note
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">that the Sample Name, Sample Data Header, and Sequence Name columns must still
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">have a unique combo value (for file validation, even though they won't be used).
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Boolean: 'skip' or ''.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Courier"/>
+            <family val="2"/>
+          </rPr>
+          <t>Optional.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -373,7 +1150,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -403,7 +1180,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -429,7 +1206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="141">
   <si>
     <t>Infusate</t>
   </si>
@@ -839,6 +1616,63 @@
   <si>
     <t>Xianfeng Zeng, polar-HILIC-25-min, unknown, 1972-11-24</t>
   </si>
+  <si>
+    <t>Sample Name</t>
+  </si>
+  <si>
+    <t>Sample Data Header</t>
+  </si>
+  <si>
+    <t>mzXML File Name</t>
+  </si>
+  <si>
+    <t>Peak Annotation File Name</t>
+  </si>
+  <si>
+    <t>Sequence Name</t>
+  </si>
+  <si>
+    <t>Skip</t>
+  </si>
+  <si>
+    <t>small_obob_maven_6eaas_inf_req_prefix.xlsx</t>
+  </si>
+  <si>
+    <t>Operator</t>
+  </si>
+  <si>
+    <t>LC Protocol Name</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>polar-HILIC-25-min</t>
+  </si>
+  <si>
+    <t>unknown</t>
+  </si>
+  <si>
+    <t>1972-11-24</t>
+  </si>
+  <si>
+    <t>Study ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>A description</t>
+  </si>
+  <si>
+    <t>obob</t>
+  </si>
 </sst>
 </file>
 
@@ -847,7 +1681,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy&quot;-&quot;mm&quot;-&quot;dd"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -955,6 +1789,26 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Courier"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="81"/>
+      <name val="Courier"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -964,7 +1818,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -987,12 +1841,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1019,12 +1888,224 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{F34B0BC4-0474-5D47-93C7-FE64BAA63C00}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1234,6 +2315,57 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C61425D-F23C-6F4F-8608-324522C2138E}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="14">
+      <c r="A1" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="notContainsErrors" dxfId="7" priority="1">
+      <formula>NOT(ISERROR(A1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="notContainsErrors" dxfId="6" priority="2">
+      <formula>NOT(ISERROR(B1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1">
+    <cfRule type="notContainsErrors" dxfId="5" priority="3">
+      <formula>NOT(ISERROR(C1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2226,7 +3358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2234,12 +3366,12 @@
   <dimension ref="A1:AD1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="23.5" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" customWidth="1"/>
-    <col min="4" max="4" width="27.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" customWidth="1"/>
     <col min="8" max="8" width="17.1640625" customWidth="1"/>
     <col min="9" max="9" width="16.6640625" customWidth="1"/>
@@ -20491,7 +21623,391 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10F537B-37AF-BD4C-9F83-7496A78BD954}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="47" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="14">
+      <c r="A1" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="notContainsErrors" dxfId="4" priority="1">
+      <formula>NOT(ISERROR(A1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:E1">
+    <cfRule type="notContainsErrors" dxfId="3" priority="2">
+      <formula>NOT(ISERROR(B1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="notContainsErrors" dxfId="2" priority="3">
+      <formula>NOT(ISERROR(F1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D077B6-035D-754F-89D0-AD0330B7C482}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="63.6640625" customWidth="1"/>
+    <col min="3" max="3" width="47" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="14">
+      <c r="A1" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD2DCCD-0178-094D-9522-9414A02DC911}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="46.5" customWidth="1"/>
+    <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="14">
+      <c r="A1" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="notContainsErrors" dxfId="1" priority="1">
+      <formula>NOT(ISERROR(A1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:F1">
+    <cfRule type="notContainsErrors" dxfId="0" priority="2">
+      <formula>NOT(ISERROR(C1))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" showInputMessage="1" prompt="Each sample name must be unique" sqref="A2:B17" xr:uid="{F169F778-8480-4947-ABEB-D876FA8E756B}">
+      <formula1>COUNTIF($A:$A,"="&amp;A2)  &lt; 2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -20500,7 +22016,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="126.6640625" customWidth="1"/>
+    <col min="2" max="2" width="52.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
@@ -20558,7 +22074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -20901,43 +22417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30D077B6-035D-754F-89D0-AD0330B7C482}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
-  <cols>
-    <col min="1" max="1" width="63.6640625" customWidth="1"/>
-    <col min="3" max="3" width="43.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="14">
-      <c r="A1" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
